--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="277">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -844,6 +844,12 @@
   </si>
   <si>
     <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>1405/06/22</t>
+  </si>
+  <si>
+    <t>دنگ سس</t>
   </si>
 </sst>
 </file>
@@ -1384,7 +1390,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4874,17 +4880,23 @@
     <row r="249" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <f t="shared" ref="A249:A258" si="14">A248+B249-C249</f>
-        <v>6522000</v>
-      </c>
-      <c r="B249" s="8"/>
+        <v>6618000</v>
+      </c>
+      <c r="B249" s="8">
+        <v>96000</v>
+      </c>
       <c r="C249" s="8"/>
-      <c r="D249" s="8"/>
-      <c r="E249" s="1"/>
+      <c r="D249" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
@@ -4894,7 +4906,7 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4904,7 +4916,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4914,7 +4926,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4924,7 +4936,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4934,7 +4946,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4944,7 +4956,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4954,7 +4966,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4964,7 +4976,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4975,7 +4987,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1335000</v>
+        <v>1431000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -4993,7 +5005,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="278">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -850,6 +850,9 @@
   </si>
   <si>
     <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>1405/07/04</t>
   </si>
 </sst>
 </file>
@@ -1390,7 +1393,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4896,17 +4899,23 @@
     <row r="250" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
-      </c>
-      <c r="B250" s="8"/>
+        <v>6843000</v>
+      </c>
+      <c r="B250" s="8">
+        <v>225000</v>
+      </c>
       <c r="C250" s="8"/>
-      <c r="D250" s="8"/>
-      <c r="E250" s="1"/>
+      <c r="D250" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
@@ -4916,7 +4925,7 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4926,7 +4935,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4936,7 +4945,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4946,7 +4955,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4956,7 +4965,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4966,7 +4975,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4976,7 +4985,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4987,7 +4996,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1431000</v>
+        <v>1656000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -5005,7 +5014,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="279">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -853,6 +853,9 @@
   </si>
   <si>
     <t>1405/07/04</t>
+  </si>
+  <si>
+    <t>1405/07/06</t>
   </si>
 </sst>
 </file>
@@ -1393,7 +1396,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4915,17 +4918,23 @@
     <row r="251" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
-      </c>
-      <c r="B251" s="8"/>
+        <v>6893000</v>
+      </c>
+      <c r="B251" s="8">
+        <v>50000</v>
+      </c>
       <c r="C251" s="8"/>
-      <c r="D251" s="8"/>
-      <c r="E251" s="1"/>
+      <c r="D251" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
@@ -4935,7 +4944,7 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4945,7 +4954,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4955,7 +4964,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4965,7 +4974,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4975,7 +4984,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4985,7 +4994,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -4996,7 +5005,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1656000</v>
+        <v>1706000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -5014,7 +5023,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="281">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -856,6 +856,12 @@
   </si>
   <si>
     <t>1405/07/06</t>
+  </si>
+  <si>
+    <t>1405/07/09</t>
+  </si>
+  <si>
+    <t>وجه برگشتی سیگار</t>
   </si>
 </sst>
 </file>
@@ -1396,7 +1402,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4934,17 +4940,23 @@
     <row r="252" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <f t="shared" si="14"/>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="B252" s="8"/>
-      <c r="C252" s="8"/>
-      <c r="D252" s="8"/>
-      <c r="E252" s="1"/>
+      <c r="C252" s="8">
+        <v>238000</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
@@ -4954,7 +4966,7 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4964,7 +4976,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4974,7 +4986,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4984,7 +4996,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -4994,7 +5006,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -5009,7 +5021,7 @@
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
-        <v>0</v>
+        <v>238000</v>
       </c>
       <c r="D259" s="9"/>
     </row>
@@ -5023,7 +5035,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="282">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -862,6 +862,9 @@
   </si>
   <si>
     <t>وجه برگشتی سیگار</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
   </si>
 </sst>
 </file>
@@ -1402,7 +1405,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4956,17 +4959,23 @@
     <row r="253" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <f t="shared" si="14"/>
-        <v>6655000</v>
-      </c>
-      <c r="B253" s="8"/>
+        <v>6671000</v>
+      </c>
+      <c r="B253" s="8">
+        <v>16000</v>
+      </c>
       <c r="C253" s="8"/>
-      <c r="D253" s="8"/>
-      <c r="E253" s="1"/>
+      <c r="D253" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
@@ -4976,7 +4985,7 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4986,7 +4995,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -4996,7 +5005,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -5006,7 +5015,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -5017,7 +5026,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1706000</v>
+        <v>1722000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -5035,7 +5044,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="282">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6671000</v>
+        <v>6871000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4975,17 +4975,21 @@
     <row r="254" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <f t="shared" si="14"/>
-        <v>6671000</v>
-      </c>
-      <c r="B254" s="8"/>
+        <v>6871000</v>
+      </c>
+      <c r="B254" s="8">
+        <v>200000</v>
+      </c>
       <c r="C254" s="8"/>
-      <c r="D254" s="8"/>
+      <c r="D254" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="E254" s="1"/>
     </row>
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6671000</v>
+        <v>6871000</v>
       </c>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -4995,7 +4999,7 @@
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6671000</v>
+        <v>6871000</v>
       </c>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
@@ -5005,7 +5009,7 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6671000</v>
+        <v>6871000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -5015,7 +5019,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6671000</v>
+        <v>6871000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -5026,7 +5030,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1722000</v>
+        <v>1922000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -5044,7 +5048,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6671000</v>
+        <v>6871000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="283">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -865,6 +865,9 @@
   </si>
   <si>
     <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1408,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>6871000</v>
+        <v>7166000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4989,27 +4992,37 @@
     <row r="255" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <f t="shared" si="14"/>
-        <v>6871000</v>
-      </c>
-      <c r="B255" s="8"/>
+        <v>7096000</v>
+      </c>
+      <c r="B255" s="8">
+        <v>225000</v>
+      </c>
       <c r="C255" s="8"/>
-      <c r="D255" s="8"/>
-      <c r="E255" s="1"/>
+      <c r="D255" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="256" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <f t="shared" si="14"/>
-        <v>6871000</v>
-      </c>
-      <c r="B256" s="8"/>
+        <v>7166000</v>
+      </c>
+      <c r="B256" s="8">
+        <v>70000</v>
+      </c>
       <c r="C256" s="8"/>
-      <c r="D256" s="8"/>
+      <c r="D256" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="E256" s="1"/>
     </row>
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>6871000</v>
+        <v>7166000</v>
       </c>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
@@ -5019,7 +5032,7 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>6871000</v>
+        <v>7166000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -5030,7 +5043,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>1922000</v>
+        <v>2217000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -5048,7 +5061,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>6871000</v>
+        <v>7166000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="284">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -868,6 +868,9 @@
   </si>
   <si>
     <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>1405/07/18</t>
   </si>
 </sst>
 </file>
@@ -1408,7 +1411,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>7166000</v>
+        <v>7216000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5022,17 +5025,23 @@
     <row r="257" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <f t="shared" si="14"/>
-        <v>7166000</v>
-      </c>
-      <c r="B257" s="8"/>
+        <v>7216000</v>
+      </c>
+      <c r="B257" s="8">
+        <v>50000</v>
+      </c>
       <c r="C257" s="8"/>
-      <c r="D257" s="8"/>
-      <c r="E257" s="1"/>
+      <c r="D257" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>7166000</v>
+        <v>7216000</v>
       </c>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
@@ -5043,7 +5052,7 @@
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>2217000</v>
+        <v>2267000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -5061,7 +5070,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>7166000</v>
+        <v>7216000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="285">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -871,6 +871,9 @@
   </si>
   <si>
     <t>1405/07/18</t>
+  </si>
+  <si>
+    <t>1405/07/22</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1414,7 @@
       </c>
       <c r="H2" s="9">
         <f>B261</f>
-        <v>7216000</v>
+        <v>7266000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5041,18 +5044,24 @@
     <row r="258" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <f t="shared" si="14"/>
-        <v>7216000</v>
-      </c>
-      <c r="B258" s="8"/>
+        <v>7266000</v>
+      </c>
+      <c r="B258" s="8">
+        <v>50000</v>
+      </c>
       <c r="C258" s="8"/>
-      <c r="D258" s="8"/>
-      <c r="E258" s="1"/>
+      <c r="D258" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="259" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="9"/>
       <c r="B259" s="9">
         <f>SUM(B239:B258) +B233</f>
-        <v>2267000</v>
+        <v>2317000</v>
       </c>
       <c r="C259" s="9">
         <f>SUM(C239:C258) +C233</f>
@@ -5070,7 +5079,7 @@
       <c r="A261" s="9"/>
       <c r="B261" s="12">
         <f>A258</f>
-        <v>7216000</v>
+        <v>7266000</v>
       </c>
       <c r="C261" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="287">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -874,6 +874,12 @@
   </si>
   <si>
     <t>1405/07/22</t>
+  </si>
+  <si>
+    <t>1405/07/23</t>
+  </si>
+  <si>
+    <t>پول</t>
   </si>
 </sst>
 </file>
@@ -994,7 +1000,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1376,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H426"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -1413,8 +1440,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B261</f>
-        <v>7266000</v>
+        <f>B289</f>
+        <v>7366000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5060,12 +5087,12 @@
     <row r="259" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="9"/>
       <c r="B259" s="9">
-        <f>SUM(B239:B258) +B233</f>
-        <v>2317000</v>
+        <f>SUM(B239:B258) +B232</f>
+        <v>15670000</v>
       </c>
       <c r="C259" s="9">
-        <f>SUM(C239:C258) +C233</f>
-        <v>238000</v>
+        <f>SUM(C239:C258) +C232</f>
+        <v>8404000</v>
       </c>
       <c r="D259" s="9"/>
     </row>
@@ -5096,13 +5123,414 @@
     </row>
     <row r="263" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="264" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>10</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C265" s="2"/>
+    </row>
+    <row r="266" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D266" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="8">
+        <f>B261+B267-C267</f>
+        <v>7366000</v>
+      </c>
+      <c r="B267" s="8">
+        <v>100000</v>
+      </c>
+      <c r="C267" s="8"/>
+      <c r="D267" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="8">
+        <f>A267+B268-C268</f>
+        <v>7366000</v>
+      </c>
+      <c r="B268" s="8"/>
+      <c r="C268" s="8"/>
+      <c r="D268" s="8"/>
+      <c r="E268" s="1"/>
+    </row>
+    <row r="269" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="8">
+        <f t="shared" ref="A269:A271" si="15">A268+B269-C269</f>
+        <v>7366000</v>
+      </c>
+      <c r="B269" s="8"/>
+      <c r="C269" s="8"/>
+      <c r="D269" s="8"/>
+      <c r="E269" s="1"/>
+    </row>
+    <row r="270" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="8">
+        <f t="shared" si="15"/>
+        <v>7366000</v>
+      </c>
+      <c r="B270" s="8"/>
+      <c r="C270" s="8"/>
+      <c r="D270" s="8"/>
+      <c r="E270" s="1"/>
+    </row>
+    <row r="271" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="8">
+        <f t="shared" si="15"/>
+        <v>7366000</v>
+      </c>
+      <c r="B271" s="8"/>
+      <c r="C271" s="8"/>
+      <c r="D271" s="8"/>
+      <c r="E271" s="1"/>
+    </row>
+    <row r="272" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="8">
+        <f>A271+B272-C272</f>
+        <v>7366000</v>
+      </c>
+      <c r="B272" s="8"/>
+      <c r="C272" s="8"/>
+      <c r="D272" s="8"/>
+      <c r="E272" s="1"/>
+    </row>
+    <row r="273" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="8">
+        <f t="shared" ref="A273:A275" si="16">A272+B273-C273</f>
+        <v>7366000</v>
+      </c>
+      <c r="B273" s="8"/>
+      <c r="C273" s="8"/>
+      <c r="D273" s="8"/>
+      <c r="E273" s="1"/>
+    </row>
+    <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" s="8">
+        <f t="shared" si="16"/>
+        <v>7366000</v>
+      </c>
+      <c r="B274" s="8"/>
+      <c r="C274" s="8"/>
+      <c r="D274" s="8"/>
+      <c r="E274" s="1"/>
+    </row>
+    <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="8">
+        <f t="shared" si="16"/>
+        <v>7366000</v>
+      </c>
+      <c r="B275" s="8"/>
+      <c r="C275" s="8"/>
+      <c r="D275" s="8"/>
+      <c r="E275" s="1"/>
+    </row>
+    <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="8">
+        <f>A275+B276-C276</f>
+        <v>7366000</v>
+      </c>
+      <c r="B276" s="8"/>
+      <c r="C276" s="8"/>
+      <c r="D276" s="8"/>
+      <c r="E276" s="1"/>
+    </row>
+    <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" s="8">
+        <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
+        <v>7366000</v>
+      </c>
+      <c r="B277" s="8"/>
+      <c r="C277" s="8"/>
+      <c r="D277" s="8"/>
+      <c r="E277" s="1"/>
+    </row>
+    <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B278" s="8"/>
+      <c r="C278" s="8"/>
+      <c r="D278" s="8"/>
+      <c r="E278" s="1"/>
+    </row>
+    <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B279" s="8"/>
+      <c r="C279" s="8"/>
+      <c r="D279" s="8"/>
+      <c r="E279" s="1"/>
+    </row>
+    <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B280" s="8"/>
+      <c r="C280" s="8"/>
+      <c r="D280" s="8"/>
+      <c r="E280" s="1"/>
+    </row>
+    <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B281" s="8"/>
+      <c r="C281" s="8"/>
+      <c r="D281" s="8"/>
+      <c r="E281" s="1"/>
+    </row>
+    <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B282" s="8"/>
+      <c r="C282" s="8"/>
+      <c r="D282" s="8"/>
+      <c r="E282" s="1"/>
+    </row>
+    <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B283" s="8"/>
+      <c r="C283" s="8"/>
+      <c r="D283" s="8"/>
+      <c r="E283" s="1"/>
+    </row>
+    <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B284" s="8"/>
+      <c r="C284" s="8"/>
+      <c r="D284" s="8"/>
+      <c r="E284" s="1"/>
+    </row>
+    <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B285" s="8"/>
+      <c r="C285" s="8"/>
+      <c r="D285" s="8"/>
+      <c r="E285" s="1"/>
+    </row>
+    <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="8">
+        <f t="shared" si="17"/>
+        <v>7366000</v>
+      </c>
+      <c r="B286" s="8"/>
+      <c r="C286" s="8"/>
+      <c r="D286" s="8"/>
+      <c r="E286" s="1"/>
+    </row>
+    <row r="287" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" s="9"/>
+      <c r="B287" s="9">
+        <f>SUM(B267:B286) +B259</f>
+        <v>15770000</v>
+      </c>
+      <c r="C287" s="9">
+        <f>SUM(C267:C286) +C259</f>
+        <v>8404000</v>
+      </c>
+      <c r="D287" s="9"/>
+    </row>
+    <row r="288" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="9"/>
+      <c r="B288" s="9"/>
+      <c r="C288" s="9"/>
+      <c r="D288" s="9"/>
+    </row>
+    <row r="289" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A289" s="9"/>
+      <c r="B289" s="12">
+        <f>A286</f>
+        <v>7366000</v>
+      </c>
+      <c r="C289" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D289" s="14"/>
+    </row>
+    <row r="290" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>86</v>
+      </c>
+      <c r="D290" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="C289:D289"/>
     <mergeCell ref="C261:D261"/>
     <mergeCell ref="C234:D234"/>
     <mergeCell ref="C102:D102"/>
@@ -5112,6 +5540,17 @@
     <mergeCell ref="C208:D208"/>
   </mergeCells>
   <conditionalFormatting sqref="B156">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B182">
     <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5122,7 +5561,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B208">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5133,7 +5572,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B208">
+  <conditionalFormatting sqref="B234">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5144,7 +5583,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
+  <conditionalFormatting sqref="B261">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5155,7 +5594,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B261">
+  <conditionalFormatting sqref="B289">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5152,10 +5152,10 @@
     <row r="267" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="8">
         <f>B261+B267-C267</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B267" s="8">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="C267" s="8"/>
       <c r="D267" s="8" t="s">
@@ -5168,7 +5168,7 @@
     <row r="268" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="8">
         <f>A267+B268-C268</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B268" s="8"/>
       <c r="C268" s="8"/>
@@ -5178,7 +5178,7 @@
     <row r="269" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="8">
         <f t="shared" ref="A269:A271" si="15">A268+B269-C269</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B269" s="8"/>
       <c r="C269" s="8"/>
@@ -5188,7 +5188,7 @@
     <row r="270" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="8">
         <f t="shared" si="15"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
@@ -5198,7 +5198,7 @@
     <row r="271" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <f t="shared" si="15"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
@@ -5208,7 +5208,7 @@
     <row r="272" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <f>A271+B272-C272</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B272" s="8"/>
       <c r="C272" s="8"/>
@@ -5218,7 +5218,7 @@
     <row r="273" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <f t="shared" ref="A273:A275" si="16">A272+B273-C273</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5228,7 +5228,7 @@
     <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <f t="shared" si="16"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
@@ -5238,7 +5238,7 @@
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
@@ -5248,7 +5248,7 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5258,7 +5258,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5268,7 +5268,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5278,7 +5278,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5288,7 +5288,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5298,7 +5298,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5308,7 +5308,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5318,7 +5318,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5328,7 +5328,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5338,7 +5338,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5348,7 +5348,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5359,7 +5359,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>15770000</v>
+        <v>15870000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5377,7 +5377,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="289">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -880,6 +880,12 @@
   </si>
   <si>
     <t>پول</t>
+  </si>
+  <si>
+    <t>1405/06/23</t>
+  </si>
+  <si>
+    <t>دنگ مزه پل دو آب</t>
   </si>
 </sst>
 </file>
@@ -1441,7 +1447,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5168,27 +5174,39 @@
     <row r="268" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="8">
         <f>A267+B268-C268</f>
-        <v>7466000</v>
-      </c>
-      <c r="B268" s="8"/>
+        <v>7655000</v>
+      </c>
+      <c r="B268" s="8">
+        <v>189000</v>
+      </c>
       <c r="C268" s="8"/>
-      <c r="D268" s="8"/>
-      <c r="E268" s="1"/>
+      <c r="D268" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="269" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="8">
         <f t="shared" ref="A269:A271" si="15">A268+B269-C269</f>
-        <v>7466000</v>
-      </c>
-      <c r="B269" s="8"/>
+        <v>7680000</v>
+      </c>
+      <c r="B269" s="8">
+        <v>25000</v>
+      </c>
       <c r="C269" s="8"/>
-      <c r="D269" s="8"/>
-      <c r="E269" s="1"/>
+      <c r="D269" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="270" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="8">
         <f t="shared" si="15"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
@@ -5198,7 +5216,7 @@
     <row r="271" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <f t="shared" si="15"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
@@ -5208,7 +5226,7 @@
     <row r="272" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <f>A271+B272-C272</f>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B272" s="8"/>
       <c r="C272" s="8"/>
@@ -5218,7 +5236,7 @@
     <row r="273" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <f t="shared" ref="A273:A275" si="16">A272+B273-C273</f>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5228,7 +5246,7 @@
     <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <f t="shared" si="16"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
@@ -5238,7 +5256,7 @@
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
@@ -5248,7 +5266,7 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5258,7 +5276,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5268,7 +5286,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5278,7 +5296,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5288,7 +5306,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5298,7 +5316,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5308,7 +5326,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5318,7 +5336,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5328,7 +5346,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5338,7 +5356,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5348,7 +5366,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5359,7 +5377,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>15870000</v>
+        <v>16084000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5377,7 +5395,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="290">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -886,6 +886,9 @@
   </si>
   <si>
     <t>دنگ مزه پل دو آب</t>
+  </si>
+  <si>
+    <t>1405/07/25</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +1450,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5206,17 +5209,23 @@
     <row r="270" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="8">
         <f t="shared" si="15"/>
-        <v>7680000</v>
-      </c>
-      <c r="B270" s="8"/>
+        <v>7710000</v>
+      </c>
+      <c r="B270" s="8">
+        <v>30000</v>
+      </c>
       <c r="C270" s="8"/>
-      <c r="D270" s="8"/>
-      <c r="E270" s="1"/>
+      <c r="D270" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="271" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <f t="shared" si="15"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
@@ -5226,7 +5235,7 @@
     <row r="272" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <f>A271+B272-C272</f>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B272" s="8"/>
       <c r="C272" s="8"/>
@@ -5236,7 +5245,7 @@
     <row r="273" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <f t="shared" ref="A273:A275" si="16">A272+B273-C273</f>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5246,7 +5255,7 @@
     <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <f t="shared" si="16"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
@@ -5256,7 +5265,7 @@
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
@@ -5266,7 +5275,7 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5276,7 +5285,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5286,7 +5295,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5296,7 +5305,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5306,7 +5315,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5316,7 +5325,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5326,7 +5335,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5336,7 +5345,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5346,7 +5355,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5356,7 +5365,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5366,7 +5375,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5377,7 +5386,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>16084000</v>
+        <v>16114000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5395,7 +5404,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="291">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -889,6 +889,9 @@
   </si>
   <si>
     <t>1405/07/25</t>
+  </si>
+  <si>
+    <t>1405/07/29</t>
   </si>
 </sst>
 </file>
@@ -1450,7 +1453,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5225,27 +5228,39 @@
     <row r="271" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <f t="shared" si="15"/>
-        <v>7710000</v>
-      </c>
-      <c r="B271" s="8"/>
+        <v>7760000</v>
+      </c>
+      <c r="B271" s="8">
+        <v>50000</v>
+      </c>
       <c r="C271" s="8"/>
-      <c r="D271" s="8"/>
-      <c r="E271" s="1"/>
+      <c r="D271" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="272" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <f>A271+B272-C272</f>
-        <v>7710000</v>
-      </c>
-      <c r="B272" s="8"/>
+        <v>8030000</v>
+      </c>
+      <c r="B272" s="8">
+        <v>270000</v>
+      </c>
       <c r="C272" s="8"/>
-      <c r="D272" s="8"/>
-      <c r="E272" s="1"/>
+      <c r="D272" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="273" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <f t="shared" ref="A273:A275" si="16">A272+B273-C273</f>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5255,7 +5270,7 @@
     <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <f t="shared" si="16"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
@@ -5265,7 +5280,7 @@
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
@@ -5275,7 +5290,7 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5285,7 +5300,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5295,7 +5310,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5305,7 +5320,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5315,7 +5330,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5325,7 +5340,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5335,7 +5350,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5345,7 +5360,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5355,7 +5370,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5365,7 +5380,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5375,7 +5390,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5386,7 +5401,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>16114000</v>
+        <v>16434000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5404,7 +5419,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="292">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -892,6 +892,9 @@
   </si>
   <si>
     <t>1405/07/29</t>
+  </si>
+  <si>
+    <t>1405/07/30</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1456,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5260,17 +5263,23 @@
     <row r="273" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <f t="shared" ref="A273:A275" si="16">A272+B273-C273</f>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B273" s="8"/>
-      <c r="C273" s="8"/>
-      <c r="D273" s="8"/>
-      <c r="E273" s="1"/>
+      <c r="C273" s="8">
+        <v>3000000</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <f t="shared" si="16"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
@@ -5280,7 +5289,7 @@
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
@@ -5290,7 +5299,7 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5300,7 +5309,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5310,7 +5319,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5320,7 +5329,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5330,7 +5339,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5340,7 +5349,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5350,7 +5359,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5360,7 +5369,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5370,7 +5379,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5380,7 +5389,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5390,7 +5399,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5405,7 +5414,7 @@
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
-        <v>8404000</v>
+        <v>11404000</v>
       </c>
       <c r="D287" s="9"/>
     </row>
@@ -5419,7 +5428,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="293">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -895,6 +895,9 @@
   </si>
   <si>
     <t>1405/07/30</t>
+  </si>
+  <si>
+    <t>1405/08/04</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1459,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5279,17 +5282,23 @@
     <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <f t="shared" si="16"/>
-        <v>5030000</v>
-      </c>
-      <c r="B274" s="8"/>
+        <v>5100000</v>
+      </c>
+      <c r="B274" s="8">
+        <v>70000</v>
+      </c>
       <c r="C274" s="8"/>
-      <c r="D274" s="8"/>
-      <c r="E274" s="1"/>
+      <c r="D274" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
@@ -5299,7 +5308,7 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5309,7 +5318,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5319,7 +5328,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5329,7 +5338,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5339,7 +5348,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5349,7 +5358,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5359,7 +5368,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5369,7 +5378,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5379,7 +5388,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5389,7 +5398,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5399,7 +5408,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5410,7 +5419,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>16434000</v>
+        <v>16504000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5428,7 +5437,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="293">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5298,17 +5298,23 @@
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>5100000</v>
-      </c>
-      <c r="B275" s="8"/>
+        <v>5235000</v>
+      </c>
+      <c r="B275" s="8">
+        <v>135000</v>
+      </c>
       <c r="C275" s="8"/>
-      <c r="D275" s="8"/>
-      <c r="E275" s="1"/>
+      <c r="D275" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5318,7 +5324,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5328,7 +5334,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5338,7 +5344,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5348,7 +5354,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5358,7 +5364,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5368,7 +5374,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5378,7 +5384,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5388,7 +5394,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5398,7 +5404,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5408,7 +5414,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5419,7 +5425,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>16504000</v>
+        <v>16639000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5437,7 +5443,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="293">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5282,23 +5282,17 @@
     <row r="274" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <f t="shared" si="16"/>
-        <v>5100000</v>
-      </c>
-      <c r="B274" s="8">
-        <v>70000</v>
-      </c>
+        <v>5030000</v>
+      </c>
+      <c r="B274" s="8"/>
       <c r="C274" s="8"/>
-      <c r="D274" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>292</v>
-      </c>
+      <c r="D274" s="8"/>
+      <c r="E274" s="1"/>
     </row>
     <row r="275" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <f t="shared" si="16"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B275" s="8">
         <v>135000</v>
@@ -5314,7 +5308,7 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
@@ -5324,7 +5318,7 @@
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5334,7 +5328,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5344,7 +5338,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5354,7 +5348,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5364,7 +5358,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5374,7 +5368,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5384,7 +5378,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5394,7 +5388,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5404,7 +5398,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5414,7 +5408,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5425,7 +5419,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>16639000</v>
+        <v>16569000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5443,7 +5437,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>

--- a/customers/mohammad hosein.xlsx
+++ b/customers/mohammad hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="295">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -898,6 +898,12 @@
   </si>
   <si>
     <t>1405/08/04</t>
+  </si>
+  <si>
+    <t>1405/08/07</t>
+  </si>
+  <si>
+    <t>دنگ مزه ودکا</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1465,7 @@
       </c>
       <c r="H2" s="9">
         <f>B289</f>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5308,17 +5314,23 @@
     <row r="276" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <f>A275+B276-C276</f>
-        <v>5165000</v>
-      </c>
-      <c r="B276" s="8"/>
+        <v>5290000</v>
+      </c>
+      <c r="B276" s="8">
+        <v>125000</v>
+      </c>
       <c r="C276" s="8"/>
-      <c r="D276" s="8"/>
-      <c r="E276" s="1"/>
+      <c r="D276" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="277" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <f t="shared" ref="A277:A286" si="17">A276+B277-C277</f>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
@@ -5328,7 +5340,7 @@
     <row r="278" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
@@ -5338,7 +5350,7 @@
     <row r="279" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -5348,7 +5360,7 @@
     <row r="280" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
@@ -5358,7 +5370,7 @@
     <row r="281" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
@@ -5368,7 +5380,7 @@
     <row r="282" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
@@ -5378,7 +5390,7 @@
     <row r="283" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
@@ -5388,7 +5400,7 @@
     <row r="284" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
@@ -5398,7 +5410,7 @@
     <row r="285" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
@@ -5408,7 +5420,7 @@
     <row r="286" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <f t="shared" si="17"/>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
@@ -5419,7 +5431,7 @@
       <c r="A287" s="9"/>
       <c r="B287" s="9">
         <f>SUM(B267:B286) +B259</f>
-        <v>16569000</v>
+        <v>16694000</v>
       </c>
       <c r="C287" s="9">
         <f>SUM(C267:C286) +C259</f>
@@ -5437,7 +5449,7 @@
       <c r="A289" s="9"/>
       <c r="B289" s="12">
         <f>A286</f>
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="C289" s="13" t="s">
         <v>233</v>
